--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线4层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="432">
   <si>
     <t>ID</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>伴随着一阵刺耳的拖地声，这扇标有B-512的沉重铁门应声弹开，手电光柱如利刃般劈开室内的黑暗，跟着的着是你们紧随其后的两支枪口。</t>
+  </si>
+  <si>
+    <t>8 enhanced suspence-horror</t>
   </si>
   <si>
     <t>false</t>
@@ -2654,21 +2657,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="27" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2686,7 +2689,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2701,12 +2704,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2724,7 +2727,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2739,12 +2742,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2762,7 +2765,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2777,12 +2780,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2800,7 +2803,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2812,24 +2815,24 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="30" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2838,7 +2841,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2850,15 +2853,15 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2867,7 +2870,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2876,7 +2879,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2888,18 +2891,18 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -2914,7 +2917,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2929,15 +2932,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" ht="28.5" spans="1:12">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -2952,7 +2955,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2967,12 +2970,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2987,7 +2990,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2999,12 +3002,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3019,7 +3022,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3031,15 +3034,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="67.5" spans="1:12">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3057,7 +3060,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3072,15 +3075,15 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="28.5" spans="1:12">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3095,7 +3098,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3110,12 +3113,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3148,12 +3151,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="150" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3171,7 +3174,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3183,15 +3186,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3224,12 +3227,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="150" spans="1:12">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3247,7 +3250,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3262,15 +3265,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3285,7 +3288,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3300,15 +3303,15 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -3323,7 +3326,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3335,15 +3338,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="210" spans="1:12">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3361,7 +3364,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3376,15 +3379,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3399,7 +3402,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3414,15 +3417,15 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -3437,7 +3440,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3452,12 +3455,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3490,12 +3493,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:12">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3513,7 +3516,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3528,12 +3531,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3551,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3563,15 +3566,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3604,15 +3607,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="150" spans="1:12">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3627,7 +3630,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3642,12 +3645,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3665,7 +3668,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3680,21 +3683,21 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3703,7 +3706,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3715,15 +3718,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3732,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3741,7 +3744,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3753,18 +3756,18 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3779,7 +3782,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3794,12 +3797,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" ht="27" spans="1:12">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3817,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3829,15 +3832,15 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" ht="58.5" spans="1:12">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -3852,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3864,15 +3867,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3890,7 +3893,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3905,15 +3908,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" ht="28.5" spans="1:12">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3928,7 +3931,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3943,15 +3946,15 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
@@ -3966,7 +3969,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3981,12 +3984,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4004,7 +4007,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4019,15 +4022,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4042,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4057,12 +4060,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" ht="55.5" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4080,7 +4083,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4092,18 +4095,18 @@
         <v>15</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="150" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4118,7 +4121,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4130,15 +4133,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4156,7 +4159,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4171,12 +4174,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" ht="28.5" spans="1:12">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4194,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4209,15 +4212,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4232,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4247,12 +4250,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4270,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4285,15 +4288,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4308,7 +4311,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4323,12 +4326,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4346,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4361,12 +4364,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4384,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4399,15 +4402,15 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" ht="27" spans="1:12">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -4422,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4434,15 +4437,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" ht="150" spans="1:12">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4460,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4472,24 +4475,24 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4498,7 +4501,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4510,24 +4513,24 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4536,7 +4539,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4548,18 +4551,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4574,7 +4577,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4589,12 +4592,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4612,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4627,15 +4630,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4650,7 +4653,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4665,15 +4668,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4688,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4703,15 +4706,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4726,7 +4729,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4741,15 +4744,15 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -4764,7 +4767,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4779,12 +4782,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4802,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4817,15 +4820,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -4840,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4855,15 +4858,15 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -4878,7 +4881,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4893,12 +4896,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4916,7 +4919,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4931,15 +4934,15 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -4954,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4969,15 +4972,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -4992,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5007,12 +5010,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5030,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5045,15 +5048,15 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5068,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5083,15 +5086,15 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" ht="27" spans="1:12">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -5106,7 +5109,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5118,21 +5121,21 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5141,7 +5144,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5153,15 +5156,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" ht="54" spans="1:12">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5170,7 +5173,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5179,7 +5182,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5191,18 +5194,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" ht="90" spans="1:12">
       <c r="A70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5217,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5229,15 +5232,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" ht="90" spans="1:12">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5255,7 +5258,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5267,15 +5270,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" ht="210" spans="1:12">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5293,7 +5296,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5305,15 +5308,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" ht="90" spans="1:12">
       <c r="A73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5331,7 +5334,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5343,15 +5346,15 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L73" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" ht="150" spans="1:12">
       <c r="A74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5369,7 +5372,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5384,12 +5387,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" ht="55.5" spans="1:12">
       <c r="A75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5407,7 +5410,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5422,12 +5425,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" ht="27" spans="1:12">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5445,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5460,15 +5463,15 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -5483,7 +5486,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5498,15 +5501,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" ht="28.5" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5521,7 +5524,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5533,10 +5536,10 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5557,55 +5560,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5613,66 +5616,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -5694,616 +5697,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E22" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F22" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C23" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D23" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E23" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F23" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B24" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D24" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F24" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B25" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C25" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D25" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E25" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E27" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D28" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B30" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C31" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D31" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线4层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="433">
   <si>
     <t>ID</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>两侧墙壁上各挂着一张闪着花白乱码的监视器屏幕，粗粝的防静电橡胶垫从角落一直延伸到房门，几根断裂的线缆从天花板无力地垂下，如同被手术刀斩断的神经末梢。</t>
+  </si>
+  <si>
+    <t>unlockscene(scene7)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=2</t>
@@ -2739,15 +2742,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2765,7 +2768,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2780,12 +2783,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2803,7 +2806,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2815,24 +2818,24 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" spans="1:12">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2841,7 +2844,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2853,15 +2856,15 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2870,7 +2873,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2879,7 +2882,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2891,18 +2894,18 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -2917,7 +2920,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2932,15 +2935,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="28.5" spans="1:12">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -2955,7 +2958,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2970,12 +2973,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2990,7 +2993,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3002,12 +3005,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3022,7 +3025,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3034,15 +3037,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="67.5" spans="1:12">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3060,7 +3063,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3075,15 +3078,15 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="28.5" spans="1:12">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3098,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3113,12 +3116,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3151,12 +3154,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="150" spans="1:12">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3174,7 +3177,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3186,15 +3189,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3227,12 +3230,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="150" spans="1:12">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3250,7 +3253,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3265,15 +3268,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3288,7 +3291,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3303,15 +3306,15 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -3326,7 +3329,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3338,15 +3341,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="210" spans="1:12">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3364,7 +3367,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3379,15 +3382,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3402,7 +3405,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3417,15 +3420,15 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -3440,7 +3443,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3455,12 +3458,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3493,12 +3496,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3516,7 +3519,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3531,12 +3534,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3554,7 +3557,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3566,15 +3569,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3607,15 +3610,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="150" spans="1:12">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3630,7 +3633,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3645,12 +3648,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3668,7 +3671,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3683,21 +3686,21 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3706,7 +3709,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3718,15 +3721,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3735,7 +3738,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3744,7 +3747,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3756,18 +3759,18 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3782,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3797,12 +3800,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="27" spans="1:12">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3820,7 +3823,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3832,15 +3835,15 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="58.5" spans="1:12">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -3855,7 +3858,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3867,15 +3870,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3893,7 +3896,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3908,15 +3911,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="28.5" spans="1:12">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3931,7 +3934,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3946,15 +3949,15 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
@@ -3969,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3984,12 +3987,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4007,7 +4010,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4022,15 +4025,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4045,7 +4048,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4060,12 +4063,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="55.5" spans="1:12">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4083,7 +4086,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4095,18 +4098,18 @@
         <v>15</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="150" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4121,7 +4124,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4133,15 +4136,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="70.5" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4159,7 +4162,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4174,12 +4177,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" ht="28.5" spans="1:12">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4197,7 +4200,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4212,15 +4215,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4235,7 +4238,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4250,12 +4253,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4273,7 +4276,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4288,15 +4291,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4311,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4326,12 +4329,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4349,7 +4352,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4364,12 +4367,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4387,7 +4390,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4402,15 +4405,15 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" ht="27" spans="1:12">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -4425,7 +4428,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4437,15 +4440,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="150" spans="1:12">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4463,7 +4466,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4475,24 +4478,24 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4501,7 +4504,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4513,24 +4516,24 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4539,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4551,18 +4554,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4577,7 +4580,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4592,12 +4595,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:12">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4615,7 +4618,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4630,15 +4633,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4653,7 +4656,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4668,15 +4671,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4691,7 +4694,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4706,15 +4709,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4729,7 +4732,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4744,15 +4747,15 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -4767,7 +4770,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4782,12 +4785,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4805,7 +4808,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4820,15 +4823,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -4843,7 +4846,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4858,15 +4861,15 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -4881,7 +4884,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4896,12 +4899,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4919,7 +4922,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4934,15 +4937,15 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -4957,7 +4960,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4972,15 +4975,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -4995,7 +4998,7 @@
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5010,12 +5013,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5033,7 +5036,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5048,15 +5051,15 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5071,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5086,15 +5089,15 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" ht="27" spans="1:12">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -5109,7 +5112,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5121,21 +5124,21 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5144,7 +5147,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5156,15 +5159,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" ht="54" spans="1:12">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5173,7 +5176,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5182,7 +5185,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5194,18 +5197,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" ht="90" spans="1:12">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5220,7 +5223,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5232,15 +5235,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L70" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" ht="90" spans="1:12">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5258,7 +5261,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5270,15 +5273,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="210" spans="1:12">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5296,7 +5299,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5308,15 +5311,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L72" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" ht="90" spans="1:12">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5334,7 +5337,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5346,15 +5349,15 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" ht="150" spans="1:12">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5372,7 +5375,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5387,12 +5390,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" ht="55.5" spans="1:12">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5410,7 +5413,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5425,12 +5428,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" ht="27" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5448,7 +5451,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5463,15 +5466,15 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -5486,7 +5489,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5501,15 +5504,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" ht="28.5" spans="1:12">
       <c r="A78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5524,7 +5527,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5536,10 +5539,10 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5560,55 +5563,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5616,66 +5619,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -5697,616 +5700,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F17" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B21" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D22" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E22" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C23" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D23" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E23" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E24" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F24" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B25" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C25" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D25" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E25" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F25" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F26" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B27" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D27" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F29" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C30" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B31" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C31" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
